--- a/src/enemies_sum/moves.xlsx
+++ b/src/enemies_sum/moves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Armor\main-report\src\enemies_sum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A02A4B6-0FE2-41C8-8D92-0B1137AA76A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462DD51D-83E0-4AD6-BB60-EF3881AFC189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10920" windowHeight="14410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11190" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Частота/маска</t>
   </si>
@@ -33,28 +33,100 @@
     <t>Переміщення</t>
   </si>
   <si>
-    <t>О 07:27 відмічено прибуття другого т/з з бійцями ров</t>
-  </si>
-  <si>
-    <t>О 10:00 відмічено початок переміщення 3 в/с ров (ст. гр. УЗБЕК)</t>
-  </si>
-  <si>
-    <t>В 11:21 повз ПОЕТА мають рухатися союзники у зворотньому напрямку</t>
-  </si>
-  <si>
-    <t>В 11:35 відмічено переміщення групи (ст. гр. ГОРЕЦ)</t>
-  </si>
-  <si>
-    <t>О 12:38 відмічено переміщення групи (по огороду БТВ)</t>
-  </si>
-  <si>
-    <t>О 13:14 планується відправіляти наступну групу. в/с споряджені пончо.</t>
-  </si>
-  <si>
-    <t>О 14:00 відмічено планування переміщення групи (ст. гр. ФЕВРАЛЬ) завтра зранку до ХОМИ.</t>
-  </si>
-  <si>
-    <t>О 14:48 ЛУКИЧ та ТЕПЛИЙ перемістилися до ЖЕТОНА.</t>
+    <t>О 06:18 переміщення групи (ст. гр. МАРАТ). На зустріч можуть рухатися ЖУХА та ХОМЯК</t>
+  </si>
+  <si>
+    <t>О 06:25 СКИФ та ЛИПА будуть рухатися до ушкодженої позиції, щоб оцінити стан пошкоджень.</t>
+  </si>
+  <si>
+    <t>О 06:34 рухається група (ст. гр. АНГЕЛ)</t>
+  </si>
+  <si>
+    <t>О 07:01 рухається група (ст. гр. СЛОН)</t>
+  </si>
+  <si>
+    <t>О 07:00 2 в/с 37 мсп пройшли через позицію 36 мсп.</t>
+  </si>
+  <si>
+    <t>О 07:29 рухається група до точки Е23</t>
+  </si>
+  <si>
+    <t>О 07:36 через позицію 36 мсп буде рухатися 3 союзники.</t>
+  </si>
+  <si>
+    <t>О 08:01 готується до переміщення група (грузимся)</t>
+  </si>
+  <si>
+    <t>О 08:10 уражен штурмову двійку. Один продовжує рухатися вперед. Одягнутив пончо.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">О 08:26 до БУЛЯ рухається група. </t>
+  </si>
+  <si>
+    <t>О 08:41 рухається група (ст. гр. МЕЧ). Йдуть вздовж дороги.</t>
+  </si>
+  <si>
+    <t>О 08:45 рухається група (ст. гр. ТИГР)</t>
+  </si>
+  <si>
+    <t>О 09:39 2 в/с 37 мсп рухається через позицію 36 мсп</t>
+  </si>
+  <si>
+    <t>О 09:43 група рухається до ЕМЕЛИ.</t>
+  </si>
+  <si>
+    <t>О 09:45 руахаються 2 в/с взовж бетонки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">О 09:51 рухається група </t>
+  </si>
+  <si>
+    <t>О 09:58 рухається група (перетнули дорогу)</t>
+  </si>
+  <si>
+    <t>О 10:12 рухається група (ст. гр. ЖЕНШЕНЬ)</t>
+  </si>
+  <si>
+    <t>О 10:15 почали рухи СУДАК та ЛИПА.</t>
+  </si>
+  <si>
+    <t>О 10:18 до МАРАТА рухається група. Ще мають проходити союзники - 2 двійки</t>
+  </si>
+  <si>
+    <t>О 10:38 рухається група (йм. по інструмент) з поверненням назад.</t>
+  </si>
+  <si>
+    <t>О 10:39 починає рухатися група (ст. гр. ПЕТРУХА)</t>
+  </si>
+  <si>
+    <t>О 10:47 рухається група (ст. гр. МЕДЬ)</t>
+  </si>
+  <si>
+    <t>О 11:23 рухається група (3 в/с)</t>
+  </si>
+  <si>
+    <t>О 11:19 група вийшла від МАЙКЛА</t>
+  </si>
+  <si>
+    <t>О 11:46 група прийшла на задану точку.</t>
+  </si>
+  <si>
+    <t>О 11:50 через позицію 36 мсп рухаються 4 в/с на схід. Пройшло ще 3 в/с і ще 2 в/с рухається.</t>
+  </si>
+  <si>
+    <t>О 11:51 готується до переміщення група (ст. гр. ДЕМОН)</t>
+  </si>
+  <si>
+    <t>О 11:55 група йде на відступ.</t>
+  </si>
+  <si>
+    <t>О 11:57 рухається група до Е8 (КАЗАНА)</t>
+  </si>
+  <si>
+    <t>О 12:08 група (ст. гр. МАЙКЛ) зайшли в підвал лікарні</t>
+  </si>
+  <si>
+    <t>О 12:16 уражено підвал, де були ЯКУТ та РЕПА. Вони прийшли в інший підвал.</t>
   </si>
 </sst>
 </file>
@@ -90,8 +162,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -372,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.6328125" customWidth="1"/>
@@ -389,7 +462,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>300.346</v>
+        <v>200.232</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -397,7 +470,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>200.22399999999999</v>
+        <v>165.1</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -405,7 +478,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>200.21100000000001</v>
+        <v>300.346</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -413,7 +486,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>300.346</v>
+        <v>200.21100000000001</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -421,7 +494,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>300.346</v>
+        <v>300.36599999999999</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -429,7 +502,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>100.107</v>
+        <v>300.32</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -437,7 +510,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>200.21199999999999</v>
+        <v>300.35599999999999</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -445,10 +518,202 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>300.34699999999998</v>
+        <v>200.21199999999999</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>136.97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>147.27500000000001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>147.27500000000001</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>300.346</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>300.36599999999999</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>200.21199999999999</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>200.232</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>300.30700000000002</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>300.35300000000001</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>300.35500000000002</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>200.232</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>200.232</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>300.35300000000001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>300.34399999999999</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>147.27500000000001</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>300.35000000000002</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>200.232</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>300.32499999999999</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>300.36599999999999</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>200.232</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>300.30700000000002</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>300.32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>200.232</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>136.97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
